--- a/04_DESIGN_TABLES/DesignTable_0306.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_0306.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>OMi 0306 Bulkhead Lock Nut (Air-Way publishes ORFS FF306 only) - Design Table v1 | AW s3 double-pass 6 rows | single-source | GENERATED 2026-09-23</t>
+          <t>OMi 0306 Bulkhead Lock Nut (Air-Way publishes ORFS FF306 only) - Design Table v1 | AW s3 double-pass 6 rows | single-source | GENERATED 2026-09-23 | 2026-10-02 (group NUTS-CAPS): OMi BUILD rows filled from the OMi dimension file (one source with Brennan, ASSUMED)</t>
         </is>
       </c>
     </row>
@@ -792,24 +792,43 @@
           <t>0306-02</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1/8</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>0306-02</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5/16-24 UNF</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 17 (0306-02): Overall Length 0.22 = nut thickness (catalog W WIDTH), Hex Flat 0.562, Side 1 Thread 5/16-24 UNF, Side 1 Size 1/8" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.22, C HEX 0.562, B1 THREAD 5/16-24, TUBE O.D. 1/8 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; NOT BUILT YET (geometry, not data): no Brennan STEP with a female -02 JIC thread countersink in 09_STEP_FILES (needs BRENNAN_0306-02.stp); the generator skips this row until the -02 countersink is measured; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -829,24 +848,43 @@
           <t>0306-03</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3/16</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>0306-03</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3/8-24 UNF</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 18 (0306-03): Overall Length 0.22 = nut thickness (catalog W WIDTH), Hex Flat 0.625, Side 1 Thread 3/8-24 UNF, Side 1 Size 3/16" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.22, C HEX 0.625, B1 THREAD 3/8-24, TUBE O.D. 3/16 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -866,24 +904,43 @@
           <t>0306-04</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1/4</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>0306-04</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>7/16-20 UNF</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 19 (0306-04): Overall Length 0.28 = nut thickness (catalog W WIDTH), Hex Flat 0.687, Side 1 Thread 7/16-20 UNF, Side 1 Size 1/4" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.28, C HEX 0.687, B1 THREAD 7/16-20, TUBE O.D. 1/4 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -903,24 +960,43 @@
           <t>0306-05</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>5/16</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>0306-05</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1/2-20 UNF</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 20 (0306-05): Overall Length 0.28 = nut thickness (catalog W WIDTH), Hex Flat 0.750, Side 1 Thread 1/2-20 UNF, Side 1 Size 5/16" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.280, C HEX 0.750, B1 THREAD 1/2-20, TUBE O.D. 5/16 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -940,24 +1016,43 @@
           <t>0306-06</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3/8</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>0306-06</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>9/16-18 UNF</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 21 (0306-06): Overall Length 0.27 = nut thickness (catalog W WIDTH), Hex Flat 0.812, Side 1 Thread 9/16-18 UNF, Side 1 Size 3/8" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.27, C HEX 0.812, B1 THREAD 9/16-18, TUBE O.D. 3/8 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -977,24 +1072,43 @@
           <t>0306-08</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>0306-08</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3/4-16 UNF</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 22 (0306-08): Overall Length 0.31 = nut thickness (catalog W WIDTH), Hex Flat 1.000, Side 1 Thread 3/4-16 UNF, Side 1 Size 1/2" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.31, C HEX 1.000, B1 THREAD 3/4-16, TUBE O.D. 1/2 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1014,24 +1128,43 @@
           <t>0306-10</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5/8</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>0306-10</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>7/8-14 UNF</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 23 (0306-10): Overall Length 0.36 = nut thickness (catalog W WIDTH), Hex Flat 1.125, Side 1 Thread 7/8-14 UNF, Side 1 Size 5/8" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.36, C HEX 1.125, B1 THREAD 7/8-14, TUBE O.D. 5/8 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1051,24 +1184,43 @@
           <t>0306-12</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3/4</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>0306-12</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1 1/16-12 UNF</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 24 (0306-12): Overall Length 0.41 = nut thickness (catalog W WIDTH), Hex Flat 1.375, Side 1 Thread 1 1/16-12 UNF, Side 1 Size 3/4" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.41, C HEX 1.375, B1 THREAD 1 1/16-12, TUBE O.D. 3/4 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1088,24 +1240,43 @@
           <t>0306-16</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>0306-16</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1 5/16-12 UNF</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 26 (0306-16): Overall Length 0.41 = nut thickness (catalog W WIDTH), Hex Flat 1.625, Side 1 Thread 1 5/16-12 UNF, Side 1 Size 1" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.41, C HEX 1.625, B1 THREAD 1 5/16-12, TUBE O.D. 1 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1125,24 +1296,43 @@
           <t>0306-20</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1 1/4</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>0306-20</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1 5/8-12 UNF</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 27 (0306-20): Overall Length 0.41 = nut thickness (catalog W WIDTH), Hex Flat 1.875, Side 1 Thread 1 5/8-12 UNF, Side 1 Size 1 1/4" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.41, C HEX 1.875, B1 THREAD 1 5/8-12, TUBE O.D. 1-1/4 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1162,24 +1352,43 @@
           <t>0306-24</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1 1/2</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>0306-24</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1 7/8-12 UNF</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 28 (0306-24): Overall Length 0.41 = nut thickness (catalog W WIDTH), Hex Flat 2.125, Side 1 Thread 1 7/8-12 UNF, Side 1 Size 1 1/2" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.41, C HEX 2.125, B1 THREAD 1 7/8-12, TUBE O.D. 1-1/2 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1199,24 +1408,43 @@
           <t>0306-32</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>0306-32</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2 1/2-12 UNF</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>h2 / S4 / thread / tube OD: OMi dimension file 07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items!row 29 (0306-32): Overall Length 0.41 = nut thickness (catalog W WIDTH), Hex Flat 2.750, Side 1 Thread 2 1/2-12 UNF, Side 1 Size 2" (column mapping Q-B-OTHER-0306 answered by the Brennan catalog letters, 00_DOCS/Brennan_Catalog_2026-10-01.md); cross-check Brennan TFA catalog p65 (TFA-p065-t02, page-verified): W WIDTH 0.410, C HEX 2.750, B1 THREAD 2-1/2-12, TUBE O.D. 2 - SAME SOURCE (OMi's data are Brennan's, evidence 2026-09-26) -&gt; one source, ASSUMED; Air-Way has no JIC bulkhead locknut row (filled 2026-10-02, group NUTS-CAPS) ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): female JIC thread minor / countersink per size (JICF_MEAS, Brennan 2406 port STEPs; -03 from BRENNAN_2406-03-04); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>OMi-filled 2026-10-02 (was BUILD-MISSING: no Air-Way row): Brennan TFA catalog p65 prints the same values; single source (OMi = Brennan) -&gt; ASSUMED, a second independent source (e.g. AN929 / AN924, SAE J514/1 cap / locknut tables) would make it VERIFIED</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
